--- a/artfynd/A 35761-2025 artfynd.xlsx
+++ b/artfynd/A 35761-2025 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113701773</v>
+        <v>113701786</v>
       </c>
       <c r="B2" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>757748</v>
+        <v>757122</v>
       </c>
       <c r="R2" t="n">
-        <v>7172665</v>
+        <v>7173058</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,15 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113701777</v>
+        <v>113701772</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>757458</v>
+        <v>757790</v>
       </c>
       <c r="R3" t="n">
-        <v>7172721</v>
+        <v>7172687</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,37 +879,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113701785</v>
+        <v>113701773</v>
       </c>
       <c r="B4" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>757215</v>
+        <v>757748</v>
       </c>
       <c r="R4" t="n">
-        <v>7173028</v>
+        <v>7172665</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -996,37 +981,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113701771</v>
+        <v>113701777</v>
       </c>
       <c r="B5" t="n">
-        <v>97671</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>757783</v>
+        <v>757458</v>
       </c>
       <c r="R5" t="n">
-        <v>7172700</v>
+        <v>7172721</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,19 +1083,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113701779</v>
+        <v>113701778</v>
       </c>
       <c r="B6" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1143,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>757344</v>
+        <v>757359</v>
       </c>
       <c r="R6" t="n">
-        <v>7172897</v>
+        <v>7172843</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,19 +1185,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113701780</v>
+        <v>113701779</v>
       </c>
       <c r="B7" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1250,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>757278</v>
+        <v>757344</v>
       </c>
       <c r="R7" t="n">
-        <v>7172950</v>
+        <v>7172897</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1317,19 +1287,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113701778</v>
+        <v>113701780</v>
       </c>
       <c r="B8" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1357,10 +1322,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>757359</v>
+        <v>757278</v>
       </c>
       <c r="R8" t="n">
-        <v>7172843</v>
+        <v>7172950</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1424,37 +1389,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113701775</v>
+        <v>113701776</v>
       </c>
       <c r="B9" t="n">
-        <v>79594</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1424,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>757622</v>
+        <v>757585</v>
       </c>
       <c r="R9" t="n">
-        <v>7172699</v>
+        <v>7172651</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1531,37 +1491,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113701772</v>
+        <v>113701775</v>
       </c>
       <c r="B10" t="n">
-        <v>82248</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6464</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1571,10 +1526,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>757790</v>
+        <v>757622</v>
       </c>
       <c r="R10" t="n">
-        <v>7172687</v>
+        <v>7172699</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,37 +1593,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113701776</v>
+        <v>113701785</v>
       </c>
       <c r="B11" t="n">
-        <v>79558</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80468</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1678,10 +1628,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>757585</v>
+        <v>757215</v>
       </c>
       <c r="R11" t="n">
-        <v>7172651</v>
+        <v>7173028</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,37 +1695,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113701786</v>
+        <v>113701771</v>
       </c>
       <c r="B12" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1785,10 +1730,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>757122</v>
+        <v>757783</v>
       </c>
       <c r="R12" t="n">
-        <v>7173058</v>
+        <v>7172700</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
